--- a/data/snuskampen-master.xlsx
+++ b/data/snuskampen-master.xlsx
@@ -33730,7 +33730,7 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>Juicy Berry Stark</t>
+          <t>Juicy Berry</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">

--- a/data/snuskampen-master.xlsx
+++ b/data/snuskampen-master.xlsx
@@ -1145,7 +1145,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>G3 Blue Mint Extra Strong</t>
+          <t>Blue Mint Extra Strong</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>G3 Blue Mint Strong Superslim</t>
+          <t>Blue Mint Strong Superslim</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>G3 Extra Strong Slim</t>
+          <t>Extra Strong Slim</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>G3 Extra Strong Slim White</t>
+          <t>Extra Strong Slim White</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>G3 LOAD Super Strong Slim White Dry</t>
+          <t>LOAD Super Strong Slim White Dry</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>G3 Original Strong Slim Portionssnus</t>
+          <t>Original Strong Slim</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>G3 POW Super Strong Slim White Dry</t>
+          <t>POW Super Strong Slim White Dry</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>G3 Strong Superslim White</t>
+          <t>Strong Superslim White</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>G3 T.N.T Extra Strong Slim White</t>
+          <t>T.N.T Extra Strong Slim White</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>G3 WIRE Super Strong Slim White Dry</t>
+          <t>WIRE Super Strong Slim White Dry</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>30 Original Portionssnus</t>
+          <t>30 Original</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Original Portionssnus</t>
+          <t>Original</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Original Strong Portionssnus</t>
+          <t>Original Strong</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Salmiak Portionssnus</t>
+          <t>Salmiak</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Salmiak Strong Portionssnus</t>
+          <t>Salmiak Strong</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Signum Bergamott White Strong Portionssnus</t>
+          <t>Signum Bergamott White Strong</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Whiskey Portionssnus</t>
+          <t>Whiskey</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>77 Apple &amp; Mint</t>
+          <t>Apple &amp; Mint</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>77 Black Currant</t>
+          <t>Black Currant</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>77 Bubbly Fizz</t>
+          <t>Bubbly Fizz</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10480,7 +10480,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>77 Classic Tobacco</t>
+          <t>Classic Tobacco</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10540,7 +10540,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>77 Cola &amp; Cherry</t>
+          <t>Cola &amp; Cherry</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>77 Cola &amp; Vanilla</t>
+          <t>Cola &amp; Vanilla</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>77 Cola Ice</t>
+          <t>Cola Ice</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>77 Forest Fruits</t>
+          <t>Forest Fruits</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10780,7 +10780,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>77 Freeze Mint</t>
+          <t>Freeze Mint</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>77 Fresh Mint</t>
+          <t>Fresh Mint</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>77 Ghost Mini Cola Ice 5</t>
+          <t>Ghost Mini Cola Ice 5</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>77 Ghost Mini Original 5</t>
+          <t>Ghost Mini Original 5</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>77 Ice Mint</t>
+          <t>Ice Mint</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>77 Peach &amp; Mint</t>
+          <t>Peach &amp; Mint</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>77 Peppermint</t>
+          <t>Peppermint</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11195,7 +11195,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>77 Raspberry</t>
+          <t>Raspberry</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -11250,7 +11250,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>77 Raspberry Vanilla</t>
+          <t>Raspberry Vanilla</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>77 Salted Caramel</t>
+          <t>Salted Caramel</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>77 Sour Bliss</t>
+          <t>Sour Bliss</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>77 Strawberry</t>
+          <t>Strawberry</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>77 Tropical Mint</t>
+          <t>Tropical Mint</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>77 VB Edition Arctic Berry</t>
+          <t>VB Edition Arctic Berry</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>77 VB Edition Liquorice &amp; Citrus</t>
+          <t>VB Edition Liquorice &amp; Citrus</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>77 VB Edition Spearmint</t>
+          <t>VB Edition Spearmint</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>77 Watermelon Ice</t>
+          <t>Watermelon Ice</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">

--- a/data/snuskampen-master.xlsx
+++ b/data/snuskampen-master.xlsx
@@ -2855,7 +2855,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nej</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2901,6 +2901,11 @@
           <t>tobak</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>grov-extra-stark-portion.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="42" hidden="1">
       <c r="A42" s="2" t="inlineStr">
@@ -2970,7 +2975,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nej</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3016,6 +3021,11 @@
           <t>tobak</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>grov-white-portion.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="44" hidden="1">
       <c r="A44" s="2" t="inlineStr">
@@ -3205,7 +3215,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nej</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3251,6 +3261,11 @@
           <t>tobak</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>goteborgs-rape-hjortron-white-portion.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="48" hidden="1">
       <c r="A48" s="2" t="inlineStr">
@@ -5960,7 +5975,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nej</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6006,6 +6021,11 @@
           <t>tobak</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>ld-30-white-portion.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="94" hidden="1">
       <c r="A94" s="2" t="inlineStr">
@@ -6255,7 +6275,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>nej</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6301,6 +6321,11 @@
           <t>tobak</t>
         </is>
       </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>ld-salmiak-white-portion.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="99" hidden="1">
       <c r="A99" s="2" t="inlineStr">
@@ -6370,7 +6395,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nej</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6416,6 +6441,11 @@
           <t>tobak</t>
         </is>
       </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>ld-signum-matcha-vit.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="101" hidden="1">
       <c r="A101" s="2" t="inlineStr">
@@ -6545,7 +6575,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nej</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6591,6 +6621,11 @@
           <t>tobak</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>ld-stark-white-portion.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="104" hidden="1">
       <c r="A104" s="2" t="inlineStr">
@@ -6660,7 +6695,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>nej</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6706,6 +6741,11 @@
           <t>tobak</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>ld-white-portion.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -6715,7 +6755,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>nej</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6761,6 +6801,11 @@
           <t>tobak</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>lundgrens-aftonglod.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="107" hidden="1">
       <c r="A107" s="2" t="inlineStr">
@@ -8990,7 +9035,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>nej</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9036,6 +9081,11 @@
           <t>tobak</t>
         </is>
       </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>smalands-brukssnus-portion.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="145" hidden="1">
       <c r="A145" s="2" t="inlineStr">
@@ -17770,7 +17820,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>nej</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -17816,6 +17866,11 @@
           <t>White</t>
         </is>
       </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>fumi-salty-violet-regular-3.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="293" hidden="1">
       <c r="A293" s="2" t="inlineStr">
@@ -24830,7 +24885,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>nej</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -24876,6 +24931,11 @@
           <t>White</t>
         </is>
       </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>lundgrens-dunge.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -24885,7 +24945,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>nej</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -24929,6 +24989,11 @@
       <c r="K412" t="inlineStr">
         <is>
           <t>White</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>lundgrens-fjallskog.jpg</t>
         </is>
       </c>
     </row>
